--- a/Raw Data/two forces (40 trials)(optimized and cylindrical)/Validation(1.75).xlsx
+++ b/Raw Data/two forces (40 trials)(optimized and cylindrical)/Validation(1.75).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/SoRoSim Robots/my_robot(1.75)(3tendon)/10-03-2025/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/Raw Data/two forces (40 trials)(optimized and cylindrical)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2432" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2815DEF2-B827-474D-BCC8-F2632324398C}"/>
+  <xr:revisionPtr revIDLastSave="2435" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43FB59DF-D7D7-4BAA-9146-4CE1AC6FAB4A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
   </bookViews>
   <sheets>
     <sheet name="Proximal Validation (double)" sheetId="12" r:id="rId1"/>
@@ -521,6 +521,7 @@
     <xf numFmtId="165" fontId="5" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -566,7 +567,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -589,10 +589,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -913,68 +909,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B763EDC-8536-442D-A8D3-F37978D4DE80}">
   <dimension ref="A1:AC52"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="7.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="16" x14ac:dyDescent="0.4">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="34" t="s">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="36" t="s">
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="36"/>
+      <c r="R1" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="S1" s="37"/>
-      <c r="T1" s="37"/>
-      <c r="U1" s="37"/>
-      <c r="V1" s="37"/>
-      <c r="W1" s="37"/>
-      <c r="X1" s="38" t="s">
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
+      <c r="X1" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="Y1" s="39"/>
-      <c r="Z1" s="39"/>
-      <c r="AA1" s="39"/>
-      <c r="AB1" s="39"/>
-      <c r="AC1" s="40"/>
-    </row>
-    <row r="2" spans="1:29" ht="16" x14ac:dyDescent="0.4">
+      <c r="Y1" s="40"/>
+      <c r="Z1" s="40"/>
+      <c r="AA1" s="40"/>
+      <c r="AB1" s="40"/>
+      <c r="AC1" s="41"/>
+    </row>
+    <row r="2" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -1063,7 +1059,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="10">
         <v>0.2</v>
       </c>
@@ -1160,7 +1156,7 @@
         <v>0.16959497575759891</v>
       </c>
     </row>
-    <row r="4" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10">
         <v>1</v>
       </c>
@@ -1257,7 +1253,7 @@
         <v>3.3168251991271935E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <v>0.5</v>
       </c>
@@ -1354,7 +1350,7 @@
         <v>4.8466738080978011E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <v>0.9</v>
       </c>
@@ -1451,7 +1447,7 @@
         <v>7.3164005184173986E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="10">
         <v>0.1</v>
       </c>
@@ -1548,7 +1544,7 @@
         <v>0.16765497174263</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>0.8</v>
       </c>
@@ -1645,7 +1641,7 @@
         <v>5.6910971570014998E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <v>0.1</v>
       </c>
@@ -1742,7 +1738,7 @@
         <v>8.1221710073947906E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>0.9</v>
       </c>
@@ -1839,7 +1835,7 @@
         <v>0.10243778638839696</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <v>0.3</v>
       </c>
@@ -1936,7 +1932,7 @@
         <v>2.1234368610381971E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>0.9</v>
       </c>
@@ -2033,7 +2029,7 @@
         <v>0.33929155693054203</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="10">
         <v>0.1</v>
       </c>
@@ -2130,7 +2126,7 @@
         <v>0.1354084673881531</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <v>0.9</v>
       </c>
@@ -2227,7 +2223,7 @@
         <v>0.2541238607168198</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="10">
         <v>0.9</v>
       </c>
@@ -2324,7 +2320,7 @@
         <v>9.0605189990997009E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
         <v>0.4</v>
       </c>
@@ -2421,7 +2417,7 @@
         <v>3.2842726016044987E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <v>1</v>
       </c>
@@ -2518,7 +2514,7 @@
         <v>6.5874221420287982E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <v>0.4</v>
       </c>
@@ -2615,7 +2611,7 @@
         <v>2.7495318603516006E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
         <v>0.1</v>
       </c>
@@ -2712,7 +2708,7 @@
         <v>2.8661772584915007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <v>0.9</v>
       </c>
@@ -2809,7 +2805,7 @@
         <v>0.15892959547042801</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
         <v>0.1</v>
       </c>
@@ -2906,7 +2902,7 @@
         <v>6.7859151124950168E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <v>0.1</v>
       </c>
@@ -3003,7 +2999,7 @@
         <v>2.3799663257598969E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
         <v>0.9</v>
       </c>
@@ -3100,7 +3096,7 @@
         <v>7.7740104007720912E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <v>0.2</v>
       </c>
@@ -3197,7 +3193,7 @@
         <v>4.3655904674529955E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <v>0.6</v>
       </c>
@@ -3294,7 +3290,7 @@
         <v>3.7380270195007004E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <v>0.7</v>
       </c>
@@ -3391,7 +3387,7 @@
         <v>0.10656875114441</v>
       </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
         <v>0.1</v>
       </c>
@@ -3488,7 +3484,7 @@
         <v>2.2900347042083699E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
         <v>1</v>
       </c>
@@ -3585,7 +3581,7 @@
         <v>9.8051102924347044E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
         <v>0.7</v>
       </c>
@@ -3682,7 +3678,7 @@
         <v>0.23825191392898598</v>
       </c>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
         <v>1</v>
       </c>
@@ -3779,7 +3775,7 @@
         <v>4.9476130867003976E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A31" s="10">
         <v>0.1</v>
       </c>
@@ -3876,7 +3872,7 @@
         <v>3.1922299957275399E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
         <v>0.3</v>
       </c>
@@ -3973,7 +3969,7 @@
         <v>6.7981694507598944E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A33" s="10">
         <v>1</v>
       </c>
@@ -4070,7 +4066,7 @@
         <v>0.10296625537872006</v>
       </c>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
         <v>0.1</v>
       </c>
@@ -4167,7 +4163,7 @@
         <v>0.1380458810806271</v>
       </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A35" s="10">
         <v>0.9</v>
       </c>
@@ -4264,7 +4260,7 @@
         <v>0.11580813989639305</v>
       </c>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A36" s="10">
         <v>1</v>
       </c>
@@ -4361,7 +4357,7 @@
         <v>8.0808059692379919E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A37" s="10">
         <v>0.3</v>
       </c>
@@ -4458,7 +4454,7 @@
         <v>7.3134875679015998E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A38" s="10">
         <v>0.9</v>
       </c>
@@ -4555,7 +4551,7 @@
         <v>6.6518873405457035E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A39" s="10">
         <v>0.1</v>
       </c>
@@ -4652,7 +4648,7 @@
         <v>0.10128984146118192</v>
       </c>
     </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A40" s="10">
         <v>0.8</v>
       </c>
@@ -4749,7 +4745,7 @@
         <v>2.1069674110409942E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A41" s="10">
         <v>1</v>
       </c>
@@ -4846,7 +4842,7 @@
         <v>3.0928960800169492E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A42" s="10">
         <v>0.2</v>
       </c>
@@ -4943,7 +4939,7 @@
         <v>5.8561345481873028E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="16" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="8"/>
       <c r="B43" s="9"/>
       <c r="C43" s="8"/>
@@ -4974,7 +4970,7 @@
       <c r="AB43" s="7"/>
       <c r="AC43" s="7"/>
     </row>
-    <row r="44" spans="1:29" ht="16" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="8"/>
       <c r="B44" s="9"/>
       <c r="C44" s="8"/>
@@ -5023,7 +5019,7 @@
         <v>8.6322410710155756E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="16" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="8"/>
       <c r="B45" s="9"/>
       <c r="C45" s="8"/>
@@ -5054,7 +5050,7 @@
       <c r="AB45" s="7"/>
       <c r="AC45" s="7"/>
     </row>
-    <row r="46" spans="1:29" ht="16" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="8"/>
       <c r="B46" s="9"/>
       <c r="C46" s="8"/>
@@ -5078,14 +5074,32 @@
       <c r="U46" s="8"/>
       <c r="V46" s="8"/>
       <c r="W46" s="8"/>
-      <c r="X46" s="7"/>
-      <c r="Y46" s="7"/>
-      <c r="Z46" s="7"/>
-      <c r="AA46" s="7"/>
-      <c r="AB46" s="7"/>
-      <c r="AC46" s="7"/>
-    </row>
-    <row r="47" spans="1:29" ht="16" x14ac:dyDescent="0.4">
+      <c r="X46" s="7" cm="1">
+        <f t="array" ref="X46">SQRT(AVERAGE((L3:L42 - R3:R42)^2))</f>
+        <v>1.8147115053274948E-3</v>
+      </c>
+      <c r="Y46" s="7" cm="1">
+        <f t="array" ref="Y46">SQRT(AVERAGE((M3:M42 - S3:S42)^2))</f>
+        <v>2.4232361634779702E-2</v>
+      </c>
+      <c r="Z46" s="7" cm="1">
+        <f t="array" ref="Z46">SQRT(AVERAGE((N3:N42 - T3:T42)^2))</f>
+        <v>1.1762737759686736E-2</v>
+      </c>
+      <c r="AA46" s="7" cm="1">
+        <f t="array" ref="AA46">SQRT(AVERAGE((O3:O42 - U3:U42)^2))</f>
+        <v>9.7654080380657204E-2</v>
+      </c>
+      <c r="AB46" s="7" cm="1">
+        <f t="array" ref="AB46">SQRT(AVERAGE((P3:P42 - V3:V42)^2))</f>
+        <v>6.1301697715568322E-2</v>
+      </c>
+      <c r="AC46" s="7" cm="1">
+        <f t="array" ref="AC46">SQRT(AVERAGE((Q3:Q42 - W3:W42)^2))</f>
+        <v>0.11121743282969934</v>
+      </c>
+    </row>
+    <row r="47" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="8"/>
       <c r="B47" s="9"/>
       <c r="C47" s="8"/>
@@ -5116,7 +5130,7 @@
       <c r="AB47" s="7"/>
       <c r="AC47" s="7"/>
     </row>
-    <row r="48" spans="1:29" ht="16" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="8"/>
       <c r="B48" s="9"/>
       <c r="C48" s="8"/>
@@ -5147,7 +5161,7 @@
       <c r="AB48" s="7"/>
       <c r="AC48" s="7"/>
     </row>
-    <row r="49" spans="1:29" ht="16" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="8"/>
       <c r="B49" s="9"/>
       <c r="C49" s="8"/>
@@ -5178,7 +5192,7 @@
       <c r="AB49" s="7"/>
       <c r="AC49" s="7"/>
     </row>
-    <row r="50" spans="1:29" ht="16" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="8"/>
       <c r="B50" s="9"/>
       <c r="C50" s="8"/>
@@ -5209,7 +5223,7 @@
       <c r="AB50" s="7"/>
       <c r="AC50" s="7"/>
     </row>
-    <row r="51" spans="1:29" ht="16" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="8"/>
       <c r="B51" s="9"/>
       <c r="C51" s="8"/>
@@ -5240,7 +5254,7 @@
       <c r="AB51" s="7"/>
       <c r="AC51" s="7"/>
     </row>
-    <row r="52" spans="1:29" ht="16" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="8"/>
       <c r="B52" s="9"/>
       <c r="C52" s="8"/>
@@ -5286,62 +5300,62 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{309BE333-3BAE-4E8D-AF02-67A9E2013036}">
   <dimension ref="A1:AU52"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="11" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="15.1796875" customWidth="1"/>
-    <col min="36" max="36" width="15.26953125" customWidth="1"/>
-    <col min="37" max="39" width="16.26953125" customWidth="1"/>
+    <col min="28" max="28" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="15.140625" customWidth="1"/>
+    <col min="36" max="36" width="15.28515625" customWidth="1"/>
+    <col min="37" max="39" width="16.28515625" customWidth="1"/>
     <col min="40" max="40" width="11" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="16" x14ac:dyDescent="0.4">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="34" t="s">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="36"/>
       <c r="R1" s="25" t="s">
         <v>7</v>
       </c>
@@ -5353,33 +5367,33 @@
       <c r="X1" s="26"/>
       <c r="Y1" s="26"/>
       <c r="Z1" s="24"/>
-      <c r="AA1" s="42" t="s">
+      <c r="AA1" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="AB1" s="42"/>
-      <c r="AC1" s="42"/>
-      <c r="AD1" s="42"/>
-      <c r="AE1" s="42"/>
-      <c r="AF1" s="42"/>
-      <c r="AG1" s="42"/>
-      <c r="AH1" s="42"/>
-      <c r="AI1" s="43" t="s">
+      <c r="AB1" s="43"/>
+      <c r="AC1" s="43"/>
+      <c r="AD1" s="43"/>
+      <c r="AE1" s="43"/>
+      <c r="AF1" s="43"/>
+      <c r="AG1" s="43"/>
+      <c r="AH1" s="43"/>
+      <c r="AI1" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="AJ1" s="43"/>
-      <c r="AK1" s="43"/>
-      <c r="AL1" s="43"/>
-      <c r="AM1" s="43"/>
-      <c r="AN1" s="43"/>
-      <c r="AO1" s="43"/>
-      <c r="AP1" s="43"/>
-      <c r="AQ1" s="43"/>
-      <c r="AR1" s="43"/>
-      <c r="AS1" s="43"/>
-      <c r="AT1" s="43"/>
-      <c r="AU1" s="43"/>
-    </row>
-    <row r="2" spans="1:47" ht="16" x14ac:dyDescent="0.4">
+      <c r="AJ1" s="44"/>
+      <c r="AK1" s="44"/>
+      <c r="AL1" s="44"/>
+      <c r="AM1" s="44"/>
+      <c r="AN1" s="44"/>
+      <c r="AO1" s="44"/>
+      <c r="AP1" s="44"/>
+      <c r="AQ1" s="44"/>
+      <c r="AR1" s="44"/>
+      <c r="AS1" s="44"/>
+      <c r="AT1" s="44"/>
+      <c r="AU1" s="44"/>
+    </row>
+    <row r="2" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -5495,18 +5509,18 @@
         <v>38</v>
       </c>
       <c r="AM2" s="20"/>
-      <c r="AN2" s="41" t="s">
+      <c r="AN2" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="AO2" s="41"/>
-      <c r="AP2" s="41"/>
-      <c r="AQ2" s="41"/>
-      <c r="AR2" s="41"/>
-      <c r="AS2" s="41"/>
-      <c r="AT2" s="41"/>
-      <c r="AU2" s="41"/>
-    </row>
-    <row r="3" spans="1:47" ht="16" x14ac:dyDescent="0.4">
+      <c r="AO2" s="42"/>
+      <c r="AP2" s="42"/>
+      <c r="AQ2" s="42"/>
+      <c r="AR2" s="42"/>
+      <c r="AS2" s="42"/>
+      <c r="AT2" s="42"/>
+      <c r="AU2" s="42"/>
+    </row>
+    <row r="3" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="10">
         <f>'Proximal Validation (double)'!A3</f>
         <v>0.2</v>
@@ -5676,7 +5690,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:47" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:47" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10">
         <f>'Proximal Validation (double)'!A4</f>
         <v>1</v>
@@ -5854,7 +5868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <f>'Proximal Validation (double)'!A5</f>
         <v>0.5</v>
@@ -5999,18 +6013,18 @@
         <v>0.2</v>
       </c>
       <c r="AM5" s="22"/>
-      <c r="AN5" s="41" t="s">
+      <c r="AN5" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="AO5" s="41"/>
-      <c r="AP5" s="41"/>
-      <c r="AQ5" s="41"/>
-      <c r="AR5" s="41"/>
-      <c r="AS5" s="41"/>
-      <c r="AT5" s="41"/>
-      <c r="AU5" s="41"/>
-    </row>
-    <row r="6" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AO5" s="42"/>
+      <c r="AP5" s="42"/>
+      <c r="AQ5" s="42"/>
+      <c r="AR5" s="42"/>
+      <c r="AS5" s="42"/>
+      <c r="AT5" s="42"/>
+      <c r="AU5" s="42"/>
+    </row>
+    <row r="6" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <f>'Proximal Validation (double)'!A6</f>
         <v>0.9</v>
@@ -6170,7 +6184,7 @@
       <c r="AT6" s="21"/>
       <c r="AU6" s="21"/>
     </row>
-    <row r="7" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A7" s="10">
         <f>'Proximal Validation (double)'!A7</f>
         <v>0.1</v>
@@ -6333,7 +6347,7 @@
       <c r="AT7" s="21"/>
       <c r="AU7" s="21"/>
     </row>
-    <row r="8" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <f>'Proximal Validation (double)'!A8</f>
         <v>0.8</v>
@@ -6482,7 +6496,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <f>'Proximal Validation (double)'!A9</f>
         <v>0.1</v>
@@ -6640,7 +6654,7 @@
         <v>0.5614664099551141</v>
       </c>
     </row>
-    <row r="10" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <f>'Proximal Validation (double)'!A10</f>
         <v>0.9</v>
@@ -6789,7 +6803,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <f>'Proximal Validation (double)'!A11</f>
         <v>0.3</v>
@@ -6947,7 +6961,7 @@
         <v>0.45044866287067781</v>
       </c>
     </row>
-    <row r="12" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <f>'Proximal Validation (double)'!A12</f>
         <v>0.9</v>
@@ -7096,7 +7110,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A13" s="10">
         <f>'Proximal Validation (double)'!A13</f>
         <v>0.1</v>
@@ -7254,7 +7268,7 @@
         <v>0.46185746069729394</v>
       </c>
     </row>
-    <row r="14" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <f>'Proximal Validation (double)'!A14</f>
         <v>0.9</v>
@@ -7400,7 +7414,7 @@
       </c>
       <c r="AM14" s="31"/>
     </row>
-    <row r="15" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A15" s="10">
         <f>'Proximal Validation (double)'!A15</f>
         <v>0.9</v>
@@ -7546,7 +7560,7 @@
       </c>
       <c r="AM15" s="31"/>
     </row>
-    <row r="16" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
         <f>'Proximal Validation (double)'!A16</f>
         <v>0.4</v>
@@ -7692,7 +7706,7 @@
       </c>
       <c r="AM16" s="31"/>
     </row>
-    <row r="17" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <f>'Proximal Validation (double)'!A17</f>
         <v>1</v>
@@ -7838,7 +7852,7 @@
       </c>
       <c r="AM17" s="31"/>
     </row>
-    <row r="18" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <f>'Proximal Validation (double)'!A18</f>
         <v>0.4</v>
@@ -7984,7 +7998,7 @@
       </c>
       <c r="AM18" s="31"/>
     </row>
-    <row r="19" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
         <f>'Proximal Validation (double)'!A19</f>
         <v>0.1</v>
@@ -8130,7 +8144,7 @@
       </c>
       <c r="AM19" s="31"/>
     </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <f>'Proximal Validation (double)'!A20</f>
         <v>0.9</v>
@@ -8276,7 +8290,7 @@
       </c>
       <c r="AM20" s="31"/>
     </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
         <f>'Proximal Validation (double)'!A21</f>
         <v>0.1</v>
@@ -8422,7 +8436,7 @@
       </c>
       <c r="AM21" s="31"/>
     </row>
-    <row r="22" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <f>'Proximal Validation (double)'!A22</f>
         <v>0.1</v>
@@ -8568,7 +8582,7 @@
       </c>
       <c r="AM22" s="31"/>
     </row>
-    <row r="23" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
         <f>'Proximal Validation (double)'!A23</f>
         <v>0.9</v>
@@ -8714,7 +8728,7 @@
       </c>
       <c r="AM23" s="31"/>
     </row>
-    <row r="24" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <f>'Proximal Validation (double)'!A24</f>
         <v>0.2</v>
@@ -8860,7 +8874,7 @@
       </c>
       <c r="AM24" s="31"/>
     </row>
-    <row r="25" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <f>'Proximal Validation (double)'!A25</f>
         <v>0.6</v>
@@ -9006,7 +9020,7 @@
       </c>
       <c r="AM25" s="31"/>
     </row>
-    <row r="26" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <f>'Proximal Validation (double)'!A26</f>
         <v>0.7</v>
@@ -9152,7 +9166,7 @@
       </c>
       <c r="AM26" s="31"/>
     </row>
-    <row r="27" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
         <f>'Proximal Validation (double)'!A27</f>
         <v>0.1</v>
@@ -9298,7 +9312,7 @@
       </c>
       <c r="AM27" s="31"/>
     </row>
-    <row r="28" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
         <f>'Proximal Validation (double)'!A28</f>
         <v>1</v>
@@ -9444,7 +9458,7 @@
       </c>
       <c r="AM28" s="31"/>
     </row>
-    <row r="29" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
         <f>'Proximal Validation (double)'!A29</f>
         <v>0.7</v>
@@ -9590,7 +9604,7 @@
       </c>
       <c r="AM29" s="31"/>
     </row>
-    <row r="30" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
         <f>'Proximal Validation (double)'!A30</f>
         <v>1</v>
@@ -9736,7 +9750,7 @@
       </c>
       <c r="AM30" s="31"/>
     </row>
-    <row r="31" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A31" s="10">
         <f>'Proximal Validation (double)'!A31</f>
         <v>0.1</v>
@@ -9882,7 +9896,7 @@
       </c>
       <c r="AM31" s="31"/>
     </row>
-    <row r="32" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
         <f>'Proximal Validation (double)'!A32</f>
         <v>0.3</v>
@@ -10028,7 +10042,7 @@
       </c>
       <c r="AM32" s="31"/>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A33" s="10">
         <f>'Proximal Validation (double)'!A33</f>
         <v>1</v>
@@ -10174,7 +10188,7 @@
       </c>
       <c r="AM33" s="31"/>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
         <f>'Proximal Validation (double)'!A34</f>
         <v>0.1</v>
@@ -10320,7 +10334,7 @@
       </c>
       <c r="AM34" s="31"/>
     </row>
-    <row r="35" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A35" s="10">
         <f>'Proximal Validation (double)'!A35</f>
         <v>0.9</v>
@@ -10466,7 +10480,7 @@
       </c>
       <c r="AM35" s="31"/>
     </row>
-    <row r="36" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A36" s="10">
         <f>'Proximal Validation (double)'!A36</f>
         <v>1</v>
@@ -10612,7 +10626,7 @@
       </c>
       <c r="AM36" s="31"/>
     </row>
-    <row r="37" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A37" s="10">
         <f>'Proximal Validation (double)'!A37</f>
         <v>0.3</v>
@@ -10758,7 +10772,7 @@
       </c>
       <c r="AM37" s="31"/>
     </row>
-    <row r="38" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A38" s="10">
         <f>'Proximal Validation (double)'!A38</f>
         <v>0.9</v>
@@ -10904,7 +10918,7 @@
       </c>
       <c r="AM38" s="31"/>
     </row>
-    <row r="39" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A39" s="10">
         <f>'Proximal Validation (double)'!A39</f>
         <v>0.1</v>
@@ -11050,7 +11064,7 @@
       </c>
       <c r="AM39" s="31"/>
     </row>
-    <row r="40" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A40" s="10">
         <f>'Proximal Validation (double)'!A40</f>
         <v>0.8</v>
@@ -11196,7 +11210,7 @@
       </c>
       <c r="AM40" s="31"/>
     </row>
-    <row r="41" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A41" s="10">
         <f>'Proximal Validation (double)'!A41</f>
         <v>1</v>
@@ -11342,7 +11356,7 @@
       </c>
       <c r="AM41" s="31"/>
     </row>
-    <row r="42" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A42" s="10">
         <f>'Proximal Validation (double)'!A42</f>
         <v>0.2</v>
@@ -11488,7 +11502,7 @@
       </c>
       <c r="AM42" s="31"/>
     </row>
-    <row r="43" spans="1:39" ht="16" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
       <c r="B43" s="16"/>
       <c r="C43" s="17"/>
@@ -11516,7 +11530,7 @@
       <c r="Y43" s="19"/>
       <c r="Z43" s="19"/>
     </row>
-    <row r="44" spans="1:39" ht="16" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="12"/>
       <c r="B44" s="16"/>
       <c r="C44" s="17"/>
@@ -11544,7 +11558,7 @@
       <c r="Y44" s="19"/>
       <c r="Z44" s="19"/>
     </row>
-    <row r="45" spans="1:39" ht="16" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="12"/>
       <c r="B45" s="16"/>
       <c r="C45" s="17"/>
@@ -11572,7 +11586,7 @@
       <c r="Y45" s="19"/>
       <c r="Z45" s="19"/>
     </row>
-    <row r="46" spans="1:39" ht="16" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="12"/>
       <c r="B46" s="16"/>
       <c r="C46" s="17"/>
@@ -11600,7 +11614,7 @@
       <c r="Y46" s="19"/>
       <c r="Z46" s="19"/>
     </row>
-    <row r="47" spans="1:39" ht="16" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="12"/>
       <c r="B47" s="16"/>
       <c r="C47" s="17"/>
@@ -11628,7 +11642,7 @@
       <c r="Y47" s="19"/>
       <c r="Z47" s="19"/>
     </row>
-    <row r="48" spans="1:39" ht="16" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="12"/>
       <c r="B48" s="16"/>
       <c r="C48" s="17"/>
@@ -11656,7 +11670,7 @@
       <c r="Y48" s="19"/>
       <c r="Z48" s="19"/>
     </row>
-    <row r="49" spans="1:26" ht="16" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="12"/>
       <c r="B49" s="16"/>
       <c r="C49" s="17"/>
@@ -11684,7 +11698,7 @@
       <c r="Y49" s="19"/>
       <c r="Z49" s="19"/>
     </row>
-    <row r="50" spans="1:26" ht="16" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="12"/>
       <c r="B50" s="16"/>
       <c r="C50" s="17"/>
@@ -11712,7 +11726,7 @@
       <c r="Y50" s="19"/>
       <c r="Z50" s="19"/>
     </row>
-    <row r="51" spans="1:26" ht="16" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="12"/>
       <c r="B51" s="16"/>
       <c r="C51" s="17"/>
@@ -11740,7 +11754,7 @@
       <c r="Y51" s="19"/>
       <c r="Z51" s="19"/>
     </row>
-    <row r="52" spans="1:26" ht="16" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="12"/>
       <c r="B52" s="16"/>
       <c r="C52" s="17"/>
@@ -11785,62 +11799,62 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4833AEA3-43CF-4C24-A2E3-E852DCD96325}">
   <dimension ref="A1:AU21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="11" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="15.1796875" customWidth="1"/>
-    <col min="36" max="36" width="15.26953125" customWidth="1"/>
-    <col min="37" max="39" width="16.26953125" customWidth="1"/>
+    <col min="28" max="28" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="15.140625" customWidth="1"/>
+    <col min="36" max="36" width="15.28515625" customWidth="1"/>
+    <col min="37" max="39" width="16.28515625" customWidth="1"/>
     <col min="40" max="40" width="11" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="16" x14ac:dyDescent="0.4">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="34" t="s">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="36"/>
       <c r="R1" s="25" t="s">
         <v>7</v>
       </c>
@@ -11852,33 +11866,33 @@
       <c r="X1" s="26"/>
       <c r="Y1" s="26"/>
       <c r="Z1" s="24"/>
-      <c r="AA1" s="42" t="s">
+      <c r="AA1" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="AB1" s="42"/>
-      <c r="AC1" s="42"/>
-      <c r="AD1" s="42"/>
-      <c r="AE1" s="42"/>
-      <c r="AF1" s="42"/>
-      <c r="AG1" s="42"/>
-      <c r="AH1" s="42"/>
-      <c r="AI1" s="43" t="s">
+      <c r="AB1" s="43"/>
+      <c r="AC1" s="43"/>
+      <c r="AD1" s="43"/>
+      <c r="AE1" s="43"/>
+      <c r="AF1" s="43"/>
+      <c r="AG1" s="43"/>
+      <c r="AH1" s="43"/>
+      <c r="AI1" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="AJ1" s="43"/>
-      <c r="AK1" s="43"/>
-      <c r="AL1" s="43"/>
-      <c r="AM1" s="43"/>
-      <c r="AN1" s="43"/>
-      <c r="AO1" s="43"/>
-      <c r="AP1" s="43"/>
-      <c r="AQ1" s="43"/>
-      <c r="AR1" s="43"/>
-      <c r="AS1" s="43"/>
-      <c r="AT1" s="43"/>
-      <c r="AU1" s="43"/>
-    </row>
-    <row r="2" spans="1:47" ht="16" x14ac:dyDescent="0.4">
+      <c r="AJ1" s="44"/>
+      <c r="AK1" s="44"/>
+      <c r="AL1" s="44"/>
+      <c r="AM1" s="44"/>
+      <c r="AN1" s="44"/>
+      <c r="AO1" s="44"/>
+      <c r="AP1" s="44"/>
+      <c r="AQ1" s="44"/>
+      <c r="AR1" s="44"/>
+      <c r="AS1" s="44"/>
+      <c r="AT1" s="44"/>
+      <c r="AU1" s="44"/>
+    </row>
+    <row r="2" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -11994,18 +12008,18 @@
         <v>38</v>
       </c>
       <c r="AM2" s="20"/>
-      <c r="AN2" s="41" t="s">
+      <c r="AN2" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="AO2" s="41"/>
-      <c r="AP2" s="41"/>
-      <c r="AQ2" s="41"/>
-      <c r="AR2" s="41"/>
-      <c r="AS2" s="41"/>
-      <c r="AT2" s="41"/>
-      <c r="AU2" s="41"/>
-    </row>
-    <row r="3" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AO2" s="42"/>
+      <c r="AP2" s="42"/>
+      <c r="AQ2" s="42"/>
+      <c r="AR2" s="42"/>
+      <c r="AS2" s="42"/>
+      <c r="AT2" s="42"/>
+      <c r="AU2" s="42"/>
+    </row>
+    <row r="3" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A3" s="10">
         <f>'Proximal Validation (double)'!A10</f>
         <v>0.9</v>
@@ -12030,7 +12044,7 @@
         <f>'Proximal Validation (double)'!F10</f>
         <v>0.08</v>
       </c>
-      <c r="G3" s="47">
+      <c r="G3" s="32">
         <f>'Proximal Validation (double)'!G10</f>
         <v>4.7119999999999997</v>
       </c>
@@ -12136,7 +12150,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A4" s="10">
         <f>'Proximal Validation (double)'!A11</f>
         <v>0.3</v>
@@ -12161,7 +12175,7 @@
         <f>'Proximal Validation (double)'!F11</f>
         <v>0.08</v>
       </c>
-      <c r="G4" s="47">
+      <c r="G4" s="32">
         <f>'Proximal Validation (double)'!G11</f>
         <v>4.7119999999999997</v>
       </c>
@@ -12276,7 +12290,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="5" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <f>'Proximal Validation (double)'!A26</f>
         <v>0.7</v>
@@ -12301,7 +12315,7 @@
         <f>'Proximal Validation (double)'!F26</f>
         <v>0.04</v>
       </c>
-      <c r="G5" s="47">
+      <c r="G5" s="32">
         <f>'Proximal Validation (double)'!G26</f>
         <v>3.927</v>
       </c>
@@ -12404,7 +12418,7 @@
       </c>
       <c r="AM5" s="31"/>
     </row>
-    <row r="6" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <f>'Proximal Validation (double)'!A29</f>
         <v>0.7</v>
@@ -12429,7 +12443,7 @@
         <f>'Proximal Validation (double)'!F29</f>
         <v>0.02</v>
       </c>
-      <c r="G6" s="47">
+      <c r="G6" s="32">
         <f>'Proximal Validation (double)'!G29</f>
         <v>3.927</v>
       </c>
@@ -12532,7 +12546,7 @@
       </c>
       <c r="AM6" s="31"/>
     </row>
-    <row r="7" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A7" s="10">
         <f>'Proximal Validation (double)'!A30</f>
         <v>1</v>
@@ -12557,7 +12571,7 @@
         <f>'Proximal Validation (double)'!F30</f>
         <v>0.06</v>
       </c>
-      <c r="G7" s="47">
+      <c r="G7" s="32">
         <f>'Proximal Validation (double)'!G30</f>
         <v>3.927</v>
       </c>
@@ -12660,7 +12674,7 @@
       </c>
       <c r="AM7" s="31"/>
     </row>
-    <row r="8" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <f>'Proximal Validation (double)'!A33</f>
         <v>1</v>
@@ -12685,7 +12699,7 @@
         <f>'Proximal Validation (double)'!F33</f>
         <v>0.04</v>
       </c>
-      <c r="G8" s="47">
+      <c r="G8" s="32">
         <f>'Proximal Validation (double)'!G33</f>
         <v>4.7119999999999997</v>
       </c>
@@ -12788,7 +12802,7 @@
       </c>
       <c r="AM8" s="31"/>
     </row>
-    <row r="9" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <f>'Proximal Validation (double)'!A34</f>
         <v>0.1</v>
@@ -12813,7 +12827,7 @@
         <f>'Proximal Validation (double)'!F34</f>
         <v>0.08</v>
       </c>
-      <c r="G9" s="47">
+      <c r="G9" s="32">
         <f>'Proximal Validation (double)'!G34</f>
         <v>4.7119999999999997</v>
       </c>
@@ -12916,7 +12930,7 @@
       </c>
       <c r="AM9" s="31"/>
     </row>
-    <row r="10" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <f>'Proximal Validation (double)'!A39</f>
         <v>0.1</v>
@@ -12941,7 +12955,7 @@
         <f>'Proximal Validation (double)'!F39</f>
         <v>0.02</v>
       </c>
-      <c r="G10" s="47">
+      <c r="G10" s="32">
         <f>'Proximal Validation (double)'!G39</f>
         <v>4.7119999999999997</v>
       </c>
@@ -13044,7 +13058,7 @@
       </c>
       <c r="AM10" s="31"/>
     </row>
-    <row r="11" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <f>'Proximal Validation (double)'!A40</f>
         <v>0.8</v>
@@ -13069,7 +13083,7 @@
         <f>'Proximal Validation (double)'!F40</f>
         <v>0.06</v>
       </c>
-      <c r="G11" s="47">
+      <c r="G11" s="32">
         <f>'Proximal Validation (double)'!G40</f>
         <v>4.7119999999999997</v>
       </c>
@@ -13172,7 +13186,7 @@
       </c>
       <c r="AM11" s="31"/>
     </row>
-    <row r="12" spans="1:47" ht="16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="12"/>
       <c r="B12" s="16"/>
       <c r="C12" s="17"/>
@@ -13200,7 +13214,7 @@
       <c r="Y12" s="19"/>
       <c r="Z12" s="19"/>
     </row>
-    <row r="13" spans="1:47" ht="16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
       <c r="B13" s="16"/>
       <c r="C13" s="17"/>
@@ -13228,7 +13242,7 @@
       <c r="Y13" s="19"/>
       <c r="Z13" s="19"/>
     </row>
-    <row r="14" spans="1:47" ht="16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
       <c r="B14" s="16"/>
       <c r="C14" s="17"/>
@@ -13256,7 +13270,7 @@
       <c r="Y14" s="19"/>
       <c r="Z14" s="19"/>
     </row>
-    <row r="15" spans="1:47" ht="16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="12"/>
       <c r="B15" s="16"/>
       <c r="C15" s="17"/>
@@ -13284,7 +13298,7 @@
       <c r="Y15" s="19"/>
       <c r="Z15" s="19"/>
     </row>
-    <row r="16" spans="1:47" ht="16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="12"/>
       <c r="B16" s="16"/>
       <c r="C16" s="17"/>
@@ -13312,7 +13326,7 @@
       <c r="Y16" s="19"/>
       <c r="Z16" s="19"/>
     </row>
-    <row r="17" spans="1:26" ht="16" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="12"/>
       <c r="B17" s="16"/>
       <c r="C17" s="17"/>
@@ -13340,7 +13354,7 @@
       <c r="Y17" s="19"/>
       <c r="Z17" s="19"/>
     </row>
-    <row r="18" spans="1:26" ht="16" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="12"/>
       <c r="B18" s="16"/>
       <c r="C18" s="17"/>
@@ -13368,7 +13382,7 @@
       <c r="Y18" s="19"/>
       <c r="Z18" s="19"/>
     </row>
-    <row r="19" spans="1:26" ht="16" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="12"/>
       <c r="B19" s="16"/>
       <c r="C19" s="17"/>
@@ -13396,7 +13410,7 @@
       <c r="Y19" s="19"/>
       <c r="Z19" s="19"/>
     </row>
-    <row r="20" spans="1:26" ht="16" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="12"/>
       <c r="B20" s="16"/>
       <c r="C20" s="17"/>
@@ -13424,7 +13438,7 @@
       <c r="Y20" s="19"/>
       <c r="Z20" s="19"/>
     </row>
-    <row r="21" spans="1:26" ht="16" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="12"/>
       <c r="B21" s="16"/>
       <c r="C21" s="17"/>
@@ -13468,27 +13482,27 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048D6981-73D2-4F8C-88D7-D5FA77AC2EB0}">
   <dimension ref="A1:M44"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:13" ht="16" x14ac:dyDescent="0.4">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="46"/>
-      <c r="H1" s="44" t="s">
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="47"/>
+      <c r="H1" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="46"/>
-    </row>
-    <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="47"/>
+    </row>
+    <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>15</v>
       </c>
@@ -13526,7 +13540,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2.9205024242401099E-2</v>
       </c>
@@ -13570,7 +13584,7 @@
         <v>2.9205024242401099E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0.92483174800872803</v>
       </c>
@@ -13614,7 +13628,7 @@
         <v>0.92483174800872803</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>0.403866738080978</v>
       </c>
@@ -13658,7 +13672,7 @@
         <v>0.403866738080978</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>0.75826400518417403</v>
       </c>
@@ -13702,7 +13716,7 @@
         <v>0.75826400518417403</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>-0.43824502825737</v>
       </c>
@@ -13746,7 +13760,7 @@
         <v>-0.43824502825737</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>0.108889028429985</v>
       </c>
@@ -13790,7 +13804,7 @@
         <v>0.108889028429985</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1.80782899260521E-2</v>
       </c>
@@ -13834,7 +13848,7 @@
         <v>1.80782899260521E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>0.51686221361160301</v>
       </c>
@@ -13878,7 +13892,7 @@
         <v>0.51686221361160301</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>-0.58056563138961803</v>
       </c>
@@ -13922,7 +13936,7 @@
         <v>-0.58056563138961803</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>0.27430844306945801</v>
       </c>
@@ -13966,7 +13980,7 @@
         <v>0.27430844306945801</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>-3.6308467388153097E-2</v>
       </c>
@@ -14010,7 +14024,7 @@
         <v>-3.6308467388153097E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>4.2876139283180202E-2</v>
       </c>
@@ -14054,7 +14068,7 @@
         <v>4.2876139283180202E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>-0.18459481000900299</v>
       </c>
@@ -14098,7 +14112,7 @@
         <v>-0.18459481000900299</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>0.24705727398395499</v>
       </c>
@@ -14142,7 +14156,7 @@
         <v>0.24705727398395499</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>0.42077422142028797</v>
       </c>
@@ -14186,7 +14200,7 @@
         <v>0.42077422142028797</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>0.23870468139648399</v>
       </c>
@@ -14230,7 +14244,7 @@
         <v>0.23870468139648399</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>-0.15806177258491499</v>
       </c>
@@ -14274,7 +14288,7 @@
         <v>-0.15806177258491499</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>0.26307040452957198</v>
       </c>
@@ -14318,7 +14332,7 @@
         <v>0.26307040452957198</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>-0.20531408488750499</v>
       </c>
@@ -14362,7 +14376,7 @@
         <v>-0.20531408488750499</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>-0.54190033674240101</v>
       </c>
@@ -14406,7 +14420,7 @@
         <v>-0.54190033674240101</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>-0.70544010400772095</v>
       </c>
@@ -14450,7 +14464,7 @@
         <v>-0.70544010400772095</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>-0.29774409532547003</v>
       </c>
@@ -14494,7 +14508,7 @@
         <v>-0.29774409532547003</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>-0.93568027019500699</v>
       </c>
@@ -14538,7 +14552,7 @@
         <v>-0.93568027019500699</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>-1.0432312488555899</v>
       </c>
@@ -14582,7 +14596,7 @@
         <v>-1.0432312488555899</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>-4.6399652957916301E-2</v>
       </c>
@@ -14626,7 +14640,7 @@
         <v>-4.6399652957916301E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>-0.73725110292434703</v>
       </c>
@@ -14670,7 +14684,7 @@
         <v>-0.73725110292434703</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>-0.30814808607101402</v>
       </c>
@@ -14714,7 +14728,7 @@
         <v>-0.30814808607101402</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>-6.8177700042724595E-2</v>
       </c>
@@ -14758,7 +14772,7 @@
         <v>-6.8177700042724595E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>-0.79531830549240101</v>
       </c>
@@ -14802,7 +14816,7 @@
         <v>-0.79531830549240101</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>0.47454249858856201</v>
       </c>
@@ -14846,7 +14860,7 @@
         <v>0.47454249858856201</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>-0.949754118919373</v>
       </c>
@@ -14890,7 +14904,7 @@
         <v>-0.949754118919373</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>-0.97470813989639304</v>
       </c>
@@ -14934,7 +14948,7 @@
         <v>-0.97470813989639304</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>-1.0263080596923799</v>
       </c>
@@ -14978,7 +14992,7 @@
         <v>-1.0263080596923799</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>-0.222265124320984</v>
       </c>
@@ -15022,7 +15036,7 @@
         <v>-0.222265124320984</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>-0.63768112659454301</v>
       </c>
@@ -15066,7 +15080,7 @@
         <v>-0.63768112659454301</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>-0.99801015853881803</v>
       </c>
@@ -15110,7 +15124,7 @@
         <v>-0.99801015853881803</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>-1.1885303258895901</v>
       </c>
@@ -15154,7 +15168,7 @@
         <v>-1.1885303258895901</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>-0.66350710391998302</v>
       </c>
@@ -15198,7 +15212,7 @@
         <v>-0.66350710391998302</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>-0.207838654518127</v>
       </c>
@@ -15242,7 +15256,7 @@
         <v>-0.207838654518127</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>-1.17376625537872</v>
       </c>
@@ -15286,7 +15300,7 @@
         <v>-1.17376625537872</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>-1.0569527745246899E-2</v>
       </c>
@@ -15330,7 +15344,7 @@
         <v>-1.0569527745246899E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>-0.96642386913299605</v>
       </c>
@@ -15384,11 +15398,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15645,27 +15660,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -15690,9 +15695,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>